--- a/data/bonos_flujos.xlsx
+++ b/data/bonos_flujos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C126A148-5747-4CE7-9D62-D155F093FF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4288AF5C-3856-4CB5-81C2-6056605CED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80832C3D-9255-40D8-8540-27B2F4252002}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="70">
   <si>
     <t>codigo</t>
   </si>
@@ -185,6 +185,51 @@
   </si>
   <si>
     <t>YMCXO</t>
+  </si>
+  <si>
+    <t>S27F6</t>
+  </si>
+  <si>
+    <t>S17A6</t>
+  </si>
+  <si>
+    <t>S16M6</t>
+  </si>
+  <si>
+    <t>S30A6</t>
+  </si>
+  <si>
+    <t>S29Y6</t>
+  </si>
+  <si>
+    <t>S31L6</t>
+  </si>
+  <si>
+    <t>S31G6</t>
+  </si>
+  <si>
+    <t>S30O6</t>
+  </si>
+  <si>
+    <t>S30N6</t>
+  </si>
+  <si>
+    <t>T13F6</t>
+  </si>
+  <si>
+    <t>T30J6</t>
+  </si>
+  <si>
+    <t>T15E7</t>
+  </si>
+  <si>
+    <t>T30A7</t>
+  </si>
+  <si>
+    <t>T31Y7</t>
+  </si>
+  <si>
+    <t>T30J7</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B5F0C5-12B4-4D21-93C5-46058C3B7D14}">
-  <dimension ref="A1:J532"/>
+  <dimension ref="A1:J547"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.77734375" style="1" customWidth="1"/>
@@ -10713,22 +10758,22 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B420" s="3">
-        <v>46221</v>
+        <v>46097</v>
       </c>
       <c r="C420" s="2">
-        <v>100</v>
+        <v>104.62</v>
       </c>
       <c r="D420" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E420" s="2">
-        <v>100</v>
+        <v>104.62</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>16</v>
@@ -10736,160 +10781,160 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B421" s="3">
-        <v>46221</v>
+        <v>46129</v>
       </c>
       <c r="C421" s="2">
-        <v>100</v>
+        <v>110.13</v>
       </c>
       <c r="D421" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E421" s="2">
-        <v>0</v>
+        <v>110.13</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B422" s="3">
-        <v>46405</v>
+        <v>46080</v>
       </c>
       <c r="C422" s="2">
-        <v>100</v>
+        <v>125.84</v>
       </c>
       <c r="D422" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E422" s="2">
-        <v>0</v>
+        <v>125.84</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B423" s="3">
-        <v>46586</v>
+        <v>46171</v>
       </c>
       <c r="C423" s="2">
-        <v>100</v>
+        <v>132.04</v>
       </c>
       <c r="D423" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E423" s="2">
-        <v>0</v>
+        <v>132.04</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B424" s="3">
-        <v>46770</v>
+        <v>46142</v>
       </c>
       <c r="C424" s="2">
-        <v>100</v>
+        <v>127.49</v>
       </c>
       <c r="D424" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E424" s="2">
-        <v>0</v>
+        <v>127.49</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B425" s="3">
-        <v>46952</v>
+        <v>46356</v>
       </c>
       <c r="C425" s="2">
-        <v>100</v>
+        <v>129.88999999999999</v>
       </c>
       <c r="D425" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E425" s="2">
-        <v>0</v>
+        <v>129.88999999999999</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B426" s="3">
-        <v>47136</v>
+        <v>46325</v>
       </c>
       <c r="C426" s="2">
-        <v>100</v>
+        <v>135.28</v>
       </c>
       <c r="D426" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E426" s="2">
-        <v>0</v>
+        <v>135.28</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B427" s="3">
-        <v>47317</v>
+        <v>46265</v>
       </c>
       <c r="C427" s="2">
-        <v>100</v>
+        <v>127.06</v>
       </c>
       <c r="D427" s="2">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="E427" s="2">
-        <v>33</v>
+        <v>127.06</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>16</v>
@@ -10897,45 +10942,45 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B428" s="3">
-        <v>47501</v>
+        <v>46234</v>
       </c>
       <c r="C428" s="2">
-        <v>67</v>
+        <v>117.68</v>
       </c>
       <c r="D428" s="2">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="E428" s="2">
-        <v>0</v>
+        <v>117.68</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B429" s="3">
-        <v>47682</v>
+        <v>46066</v>
       </c>
       <c r="C429" s="2">
-        <v>67</v>
+        <v>144.97</v>
       </c>
       <c r="D429" s="2">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="E429" s="2">
-        <v>33</v>
+        <v>144.97</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>16</v>
@@ -10943,45 +10988,45 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B430" s="3">
-        <v>47866</v>
+        <v>46402</v>
       </c>
       <c r="C430" s="2">
-        <v>34</v>
+        <v>161.1</v>
       </c>
       <c r="D430" s="2">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="E430" s="2">
-        <v>0</v>
+        <v>161.1</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B431" s="3">
-        <v>48047</v>
+        <v>46507</v>
       </c>
       <c r="C431" s="2">
-        <v>34</v>
+        <v>157.34</v>
       </c>
       <c r="D431" s="2">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="E431" s="2">
-        <v>34</v>
+        <v>157.34</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>16</v>
@@ -10989,22 +11034,22 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B432" s="3">
-        <v>46151</v>
+        <v>46203</v>
       </c>
       <c r="C432" s="2">
-        <v>40</v>
+        <v>144.9</v>
       </c>
       <c r="D432" s="2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E432" s="2">
-        <v>20</v>
+        <v>144.9</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>16</v>
@@ -11012,22 +11057,22 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B433" s="3">
-        <v>46335</v>
+        <v>46568</v>
       </c>
       <c r="C433" s="2">
-        <v>20</v>
+        <v>156.04</v>
       </c>
       <c r="D433" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E433" s="2">
-        <v>20</v>
+        <v>156.04</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>16</v>
@@ -11035,62 +11080,62 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B434" s="3">
-        <v>46122</v>
+        <v>46538</v>
       </c>
       <c r="C434" s="2">
-        <v>100</v>
+        <v>151.36000000000001</v>
       </c>
       <c r="D434" s="2">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="E434" s="2">
-        <v>0</v>
+        <v>151.36000000000001</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B435" s="3">
-        <v>46305</v>
+        <v>46221</v>
       </c>
       <c r="C435" s="2">
         <v>100</v>
       </c>
       <c r="D435" s="2">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="E435" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F435" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B436" s="3">
-        <v>46487</v>
+        <v>46221</v>
       </c>
       <c r="C436" s="2">
         <v>100</v>
       </c>
       <c r="D436" s="2">
-        <v>3.81</v>
+        <v>4.75</v>
       </c>
       <c r="E436" s="2">
         <v>0</v>
@@ -11104,16 +11149,16 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B437" s="3">
-        <v>46670</v>
+        <v>46405</v>
       </c>
       <c r="C437" s="2">
         <v>100</v>
       </c>
       <c r="D437" s="2">
-        <v>3.84</v>
+        <v>4.75</v>
       </c>
       <c r="E437" s="2">
         <v>0</v>
@@ -11127,16 +11172,16 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B438" s="3">
-        <v>46853</v>
+        <v>46586</v>
       </c>
       <c r="C438" s="2">
         <v>100</v>
       </c>
       <c r="D438" s="2">
-        <v>3.84</v>
+        <v>4.75</v>
       </c>
       <c r="E438" s="2">
         <v>0</v>
@@ -11150,16 +11195,16 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B439" s="3">
-        <v>47036</v>
+        <v>46770</v>
       </c>
       <c r="C439" s="2">
         <v>100</v>
       </c>
       <c r="D439" s="2">
-        <v>3.84</v>
+        <v>4.75</v>
       </c>
       <c r="E439" s="2">
         <v>0</v>
@@ -11173,16 +11218,16 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B440" s="3">
-        <v>47218</v>
+        <v>46952</v>
       </c>
       <c r="C440" s="2">
         <v>100</v>
       </c>
       <c r="D440" s="2">
-        <v>3.81</v>
+        <v>4.75</v>
       </c>
       <c r="E440" s="2">
         <v>0</v>
@@ -11196,200 +11241,200 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B441" s="3">
-        <v>47401</v>
+        <v>47136</v>
       </c>
       <c r="C441" s="2">
         <v>100</v>
       </c>
       <c r="D441" s="2">
-        <v>3.84</v>
+        <v>4.75</v>
       </c>
       <c r="E441" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F441" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B442" s="3">
-        <v>47583</v>
+        <v>47317</v>
       </c>
       <c r="C442" s="2">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D442" s="2">
-        <v>2.56</v>
+        <v>4.75</v>
       </c>
       <c r="E442" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B443" s="3">
-        <v>47766</v>
+        <v>47501</v>
       </c>
       <c r="C443" s="2">
         <v>67</v>
       </c>
       <c r="D443" s="2">
-        <v>2.57</v>
+        <v>3.18</v>
       </c>
       <c r="E443" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B444" s="3">
-        <v>47948</v>
+        <v>47682</v>
       </c>
       <c r="C444" s="2">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D444" s="2">
-        <v>1.3</v>
+        <v>3.18</v>
       </c>
       <c r="E444" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F444" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B445" s="3">
-        <v>48131</v>
+        <v>47866</v>
       </c>
       <c r="C445" s="2">
         <v>34</v>
       </c>
       <c r="D445" s="2">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="E445" s="2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F445" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B446" s="3">
-        <v>46183</v>
+        <v>48047</v>
       </c>
       <c r="C446" s="2">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D446" s="2">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="E446" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F446" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B447" s="3">
-        <v>46366</v>
+        <v>46151</v>
       </c>
       <c r="C447" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D447" s="2">
-        <v>3.82</v>
+        <v>0.4</v>
       </c>
       <c r="E447" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B448" s="3">
-        <v>46548</v>
+        <v>46335</v>
       </c>
       <c r="C448" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D448" s="2">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="E448" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B449" s="3">
-        <v>46731</v>
+        <v>46122</v>
       </c>
       <c r="C449" s="2">
         <v>100</v>
       </c>
       <c r="D449" s="2">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="E449" s="2">
         <v>0</v>
@@ -11403,16 +11448,16 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B450" s="3">
-        <v>46914</v>
+        <v>46305</v>
       </c>
       <c r="C450" s="2">
         <v>100</v>
       </c>
       <c r="D450" s="2">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="E450" s="2">
         <v>0</v>
@@ -11426,16 +11471,16 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B451" s="3">
-        <v>47097</v>
+        <v>46487</v>
       </c>
       <c r="C451" s="2">
         <v>100</v>
       </c>
       <c r="D451" s="2">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="E451" s="2">
         <v>0</v>
@@ -11449,16 +11494,16 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B452" s="3">
-        <v>47279</v>
+        <v>46670</v>
       </c>
       <c r="C452" s="2">
         <v>100</v>
       </c>
       <c r="D452" s="2">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="E452" s="2">
         <v>0</v>
@@ -11472,16 +11517,16 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B453" s="3">
-        <v>47462</v>
+        <v>46853</v>
       </c>
       <c r="C453" s="2">
         <v>100</v>
       </c>
       <c r="D453" s="2">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="E453" s="2">
         <v>0</v>
@@ -11495,16 +11540,16 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B454" s="3">
-        <v>47644</v>
+        <v>47036</v>
       </c>
       <c r="C454" s="2">
         <v>100</v>
       </c>
       <c r="D454" s="2">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="E454" s="2">
         <v>0</v>
@@ -11518,16 +11563,16 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B455" s="3">
-        <v>47827</v>
+        <v>47218</v>
       </c>
       <c r="C455" s="2">
         <v>100</v>
       </c>
       <c r="D455" s="2">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="E455" s="2">
         <v>0</v>
@@ -11541,39 +11586,39 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B456" s="3">
-        <v>48009</v>
+        <v>47401</v>
       </c>
       <c r="C456" s="2">
         <v>100</v>
       </c>
       <c r="D456" s="2">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="E456" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B457" s="3">
-        <v>48192</v>
+        <v>47583</v>
       </c>
       <c r="C457" s="2">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D457" s="2">
-        <v>3.82</v>
+        <v>2.56</v>
       </c>
       <c r="E457" s="2">
         <v>0</v>
@@ -11587,39 +11632,39 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B458" s="3">
-        <v>48375</v>
+        <v>47766</v>
       </c>
       <c r="C458" s="2">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D458" s="2">
-        <v>3.82</v>
+        <v>2.57</v>
       </c>
       <c r="E458" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F458" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B459" s="3">
-        <v>48558</v>
+        <v>47948</v>
       </c>
       <c r="C459" s="2">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D459" s="2">
-        <v>3.82</v>
+        <v>1.3</v>
       </c>
       <c r="E459" s="2">
         <v>0</v>
@@ -11633,25 +11678,25 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B460" s="3">
-        <v>48740</v>
+        <v>48131</v>
       </c>
       <c r="C460" s="2">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D460" s="2">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="E460" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F460" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,22 +11704,22 @@
         <v>48</v>
       </c>
       <c r="B461" s="3">
-        <v>48923</v>
+        <v>46183</v>
       </c>
       <c r="C461" s="2">
         <v>100</v>
       </c>
       <c r="D461" s="2">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="E461" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,13 +11727,13 @@
         <v>48</v>
       </c>
       <c r="B462" s="3">
-        <v>49105</v>
+        <v>46366</v>
       </c>
       <c r="C462" s="2">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D462" s="2">
-        <v>2.5499999999999998</v>
+        <v>3.82</v>
       </c>
       <c r="E462" s="2">
         <v>0</v>
@@ -11705,22 +11750,22 @@
         <v>48</v>
       </c>
       <c r="B463" s="3">
-        <v>49288</v>
+        <v>46548</v>
       </c>
       <c r="C463" s="2">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D463" s="2">
-        <v>2.56</v>
+        <v>3.8</v>
       </c>
       <c r="E463" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F463" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,13 +11773,13 @@
         <v>48</v>
       </c>
       <c r="B464" s="3">
-        <v>49470</v>
+        <v>46731</v>
       </c>
       <c r="C464" s="2">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D464" s="2">
-        <v>1.29</v>
+        <v>3.82</v>
       </c>
       <c r="E464" s="2">
         <v>0</v>
@@ -11751,36 +11796,36 @@
         <v>48</v>
       </c>
       <c r="B465" s="3">
-        <v>49653</v>
+        <v>46914</v>
       </c>
       <c r="C465" s="2">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D465" s="2">
-        <v>1.3</v>
+        <v>3.82</v>
       </c>
       <c r="E465" s="2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B466" s="3">
-        <v>46128</v>
+        <v>47097</v>
       </c>
       <c r="C466" s="2">
         <v>100</v>
       </c>
       <c r="D466" s="2">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="E466" s="2">
         <v>0</v>
@@ -11794,16 +11839,16 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B467" s="3">
-        <v>46311</v>
+        <v>47279</v>
       </c>
       <c r="C467" s="2">
         <v>100</v>
       </c>
       <c r="D467" s="2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="E467" s="2">
         <v>0</v>
@@ -11817,16 +11862,16 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B468" s="3">
-        <v>46493</v>
+        <v>47462</v>
       </c>
       <c r="C468" s="2">
         <v>100</v>
       </c>
       <c r="D468" s="2">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="E468" s="2">
         <v>0</v>
@@ -11840,16 +11885,16 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B469" s="3">
-        <v>46676</v>
+        <v>47644</v>
       </c>
       <c r="C469" s="2">
         <v>100</v>
       </c>
       <c r="D469" s="2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="E469" s="2">
         <v>0</v>
@@ -11863,16 +11908,16 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B470" s="3">
-        <v>46859</v>
+        <v>47827</v>
       </c>
       <c r="C470" s="2">
         <v>100</v>
       </c>
       <c r="D470" s="2">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="E470" s="2">
         <v>0</v>
@@ -11886,16 +11931,16 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B471" s="3">
-        <v>47042</v>
+        <v>48009</v>
       </c>
       <c r="C471" s="2">
         <v>100</v>
       </c>
       <c r="D471" s="2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="E471" s="2">
         <v>0</v>
@@ -11909,16 +11954,16 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B472" s="3">
-        <v>47224</v>
+        <v>48192</v>
       </c>
       <c r="C472" s="2">
         <v>100</v>
       </c>
       <c r="D472" s="2">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="E472" s="2">
         <v>0</v>
@@ -11932,16 +11977,16 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B473" s="3">
-        <v>47407</v>
+        <v>48375</v>
       </c>
       <c r="C473" s="2">
         <v>100</v>
       </c>
       <c r="D473" s="2">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="E473" s="2">
         <v>0</v>
@@ -11955,16 +12000,16 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B474" s="3">
-        <v>47589</v>
+        <v>48558</v>
       </c>
       <c r="C474" s="2">
         <v>100</v>
       </c>
       <c r="D474" s="2">
-        <v>3.93</v>
+        <v>3.82</v>
       </c>
       <c r="E474" s="2">
         <v>0</v>
@@ -11978,154 +12023,154 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B475" s="3">
-        <v>47772</v>
+        <v>48740</v>
       </c>
       <c r="C475" s="2">
         <v>100</v>
       </c>
       <c r="D475" s="2">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="E475" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B476" s="3">
-        <v>47954</v>
+        <v>48923</v>
       </c>
       <c r="C476" s="2">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D476" s="2">
-        <v>2.63</v>
+        <v>3.82</v>
       </c>
       <c r="E476" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F476" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B477" s="3">
-        <v>48137</v>
+        <v>49105</v>
       </c>
       <c r="C477" s="2">
         <v>67</v>
       </c>
       <c r="D477" s="2">
-        <v>2.65</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E477" s="2">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B478" s="3">
-        <v>48320</v>
+        <v>49288</v>
       </c>
       <c r="C478" s="2">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D478" s="2">
-        <v>1.34</v>
+        <v>2.56</v>
       </c>
       <c r="E478" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B479" s="3">
-        <v>48503</v>
+        <v>49470</v>
       </c>
       <c r="C479" s="2">
         <v>34</v>
       </c>
       <c r="D479" s="2">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="E479" s="2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B480" s="3">
-        <v>46220</v>
+        <v>49653</v>
       </c>
       <c r="C480" s="2">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D480" s="2">
-        <v>4.09</v>
+        <v>1.3</v>
       </c>
       <c r="E480" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B481" s="3">
-        <v>46404</v>
+        <v>46128</v>
       </c>
       <c r="C481" s="2">
         <v>100</v>
       </c>
       <c r="D481" s="2">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="E481" s="2">
         <v>0</v>
@@ -12139,16 +12184,16 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B482" s="3">
-        <v>46585</v>
+        <v>46311</v>
       </c>
       <c r="C482" s="2">
         <v>100</v>
       </c>
       <c r="D482" s="2">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="E482" s="2">
         <v>0</v>
@@ -12162,16 +12207,16 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B483" s="3">
-        <v>46769</v>
+        <v>46493</v>
       </c>
       <c r="C483" s="2">
         <v>100</v>
       </c>
       <c r="D483" s="2">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="E483" s="2">
         <v>0</v>
@@ -12185,16 +12230,16 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B484" s="3">
-        <v>46951</v>
+        <v>46676</v>
       </c>
       <c r="C484" s="2">
         <v>100</v>
       </c>
       <c r="D484" s="2">
-        <v>4.1100000000000003</v>
+        <v>3.95</v>
       </c>
       <c r="E484" s="2">
         <v>0</v>
@@ -12208,16 +12253,16 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B485" s="3">
-        <v>47135</v>
+        <v>46859</v>
       </c>
       <c r="C485" s="2">
         <v>100</v>
       </c>
       <c r="D485" s="2">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="E485" s="2">
         <v>0</v>
@@ -12231,16 +12276,16 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B486" s="3">
-        <v>47316</v>
+        <v>47042</v>
       </c>
       <c r="C486" s="2">
         <v>100</v>
       </c>
       <c r="D486" s="2">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="E486" s="2">
         <v>0</v>
@@ -12254,16 +12299,16 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B487" s="3">
-        <v>47500</v>
+        <v>47224</v>
       </c>
       <c r="C487" s="2">
         <v>100</v>
       </c>
       <c r="D487" s="2">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="E487" s="2">
         <v>0</v>
@@ -12277,16 +12322,16 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B488" s="3">
-        <v>47681</v>
+        <v>47407</v>
       </c>
       <c r="C488" s="2">
         <v>100</v>
       </c>
       <c r="D488" s="2">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="E488" s="2">
         <v>0</v>
@@ -12300,16 +12345,16 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B489" s="3">
-        <v>47865</v>
+        <v>47589</v>
       </c>
       <c r="C489" s="2">
         <v>100</v>
       </c>
       <c r="D489" s="2">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="E489" s="2">
         <v>0</v>
@@ -12323,117 +12368,117 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B490" s="3">
-        <v>48046</v>
+        <v>47772</v>
       </c>
       <c r="C490" s="2">
         <v>100</v>
       </c>
       <c r="D490" s="2">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="E490" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B491" s="3">
-        <v>48230</v>
+        <v>47954</v>
       </c>
       <c r="C491" s="2">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D491" s="2">
-        <v>4.16</v>
+        <v>2.63</v>
       </c>
       <c r="E491" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B492" s="3">
-        <v>48412</v>
+        <v>48137</v>
       </c>
       <c r="C492" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D492" s="2">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="E492" s="2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F492" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B493" s="3">
-        <v>48596</v>
+        <v>48320</v>
       </c>
       <c r="C493" s="2">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D493" s="2">
-        <v>2.91</v>
+        <v>1.34</v>
       </c>
       <c r="E493" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B494" s="3">
-        <v>48777</v>
+        <v>48503</v>
       </c>
       <c r="C494" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D494" s="2">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="E494" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
@@ -12441,197 +12486,197 @@
         <v>50</v>
       </c>
       <c r="B495" s="3">
-        <v>48961</v>
+        <v>46220</v>
       </c>
       <c r="C495" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D495" s="2">
-        <v>1.66</v>
+        <v>4.09</v>
       </c>
       <c r="E495" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B496" s="3">
-        <v>46203</v>
+        <v>46404</v>
       </c>
       <c r="C496" s="2">
         <v>100</v>
       </c>
       <c r="D496" s="2">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="E496" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F496" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B497" s="3">
-        <v>46386</v>
+        <v>46585</v>
       </c>
       <c r="C497" s="2">
-        <v>85.715000000000003</v>
+        <v>100</v>
       </c>
       <c r="D497" s="2">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="E497" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B498" s="3">
-        <v>46568</v>
+        <v>46769</v>
       </c>
       <c r="C498" s="2">
-        <v>71.430000000000007</v>
+        <v>100</v>
       </c>
       <c r="D498" s="2">
-        <v>3.21</v>
+        <v>4.16</v>
       </c>
       <c r="E498" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F498" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B499" s="3">
-        <v>46751</v>
+        <v>46951</v>
       </c>
       <c r="C499" s="2">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="D499" s="2">
-        <v>2.57</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="E499" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B500" s="3">
-        <v>46934</v>
+        <v>47135</v>
       </c>
       <c r="C500" s="2">
-        <v>42.86</v>
+        <v>100</v>
       </c>
       <c r="D500" s="2">
-        <v>1.93</v>
+        <v>4.16</v>
       </c>
       <c r="E500" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B501" s="3">
-        <v>47117</v>
+        <v>47316</v>
       </c>
       <c r="C501" s="2">
-        <v>28.57</v>
+        <v>100</v>
       </c>
       <c r="D501" s="2">
-        <v>1.29</v>
+        <v>4.09</v>
       </c>
       <c r="E501" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B502" s="3">
-        <v>47299</v>
+        <v>47500</v>
       </c>
       <c r="C502" s="2">
-        <v>14.29</v>
+        <v>100</v>
       </c>
       <c r="D502" s="2">
-        <v>0.64</v>
+        <v>4.16</v>
       </c>
       <c r="E502" s="2">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B503" s="3">
-        <v>46111</v>
+        <v>47681</v>
       </c>
       <c r="C503" s="2">
         <v>100</v>
       </c>
       <c r="D503" s="2">
-        <v>3.5</v>
+        <v>4.09</v>
       </c>
       <c r="E503" s="2">
         <v>0</v>
@@ -12645,16 +12690,16 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B504" s="3">
-        <v>46295</v>
+        <v>47865</v>
       </c>
       <c r="C504" s="2">
         <v>100</v>
       </c>
       <c r="D504" s="2">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="E504" s="2">
         <v>0</v>
@@ -12668,16 +12713,16 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B505" s="3">
-        <v>46476</v>
+        <v>48046</v>
       </c>
       <c r="C505" s="2">
         <v>100</v>
       </c>
       <c r="D505" s="2">
-        <v>3.5</v>
+        <v>4.09</v>
       </c>
       <c r="E505" s="2">
         <v>0</v>
@@ -12691,39 +12736,39 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B506" s="3">
-        <v>46660</v>
+        <v>48230</v>
       </c>
       <c r="C506" s="2">
         <v>100</v>
       </c>
       <c r="D506" s="2">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="E506" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B507" s="3">
-        <v>46842</v>
+        <v>48412</v>
       </c>
       <c r="C507" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D507" s="2">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="E507" s="2">
         <v>0</v>
@@ -12737,39 +12782,39 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B508" s="3">
-        <v>47026</v>
+        <v>48596</v>
       </c>
       <c r="C508" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D508" s="2">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="E508" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B509" s="3">
-        <v>47207</v>
+        <v>48777</v>
       </c>
       <c r="C509" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D509" s="2">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="E509" s="2">
         <v>0</v>
@@ -12783,65 +12828,65 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B510" s="3">
-        <v>47391</v>
+        <v>48961</v>
       </c>
       <c r="C510" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D510" s="2">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="E510" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B511" s="3">
-        <v>47572</v>
+        <v>46203</v>
       </c>
       <c r="C511" s="2">
         <v>100</v>
       </c>
       <c r="D511" s="2">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E511" s="2">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G511" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B512" s="3">
-        <v>47756</v>
+        <v>46386</v>
       </c>
       <c r="C512" s="2">
-        <v>100</v>
+        <v>85.715000000000003</v>
       </c>
       <c r="D512" s="2">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="E512" s="2">
-        <v>25</v>
+        <v>14.28</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>8</v>
@@ -12852,42 +12897,42 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B513" s="3">
-        <v>47937</v>
+        <v>46568</v>
       </c>
       <c r="C513" s="2">
-        <v>75</v>
+        <v>71.430000000000007</v>
       </c>
       <c r="D513" s="2">
-        <v>2.62</v>
+        <v>3.21</v>
       </c>
       <c r="E513" s="2">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G513" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B514" s="3">
-        <v>48121</v>
+        <v>46751</v>
       </c>
       <c r="C514" s="2">
-        <v>75</v>
+        <v>57.14</v>
       </c>
       <c r="D514" s="2">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="E514" s="2">
-        <v>25</v>
+        <v>14.28</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>8</v>
@@ -12898,42 +12943,42 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B515" s="3">
-        <v>48303</v>
+        <v>46934</v>
       </c>
       <c r="C515" s="2">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="D515" s="2">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="E515" s="2">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G515" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B516" s="3">
-        <v>48487</v>
+        <v>47117</v>
       </c>
       <c r="C516" s="2">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="D516" s="2">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="E516" s="2">
-        <v>25</v>
+        <v>14.28</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>8</v>
@@ -12944,25 +12989,25 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B517" s="3">
-        <v>48668</v>
+        <v>47299</v>
       </c>
       <c r="C517" s="2">
-        <v>25</v>
+        <v>14.29</v>
       </c>
       <c r="D517" s="2">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="E517" s="2">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G517" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
@@ -12970,36 +13015,36 @@
         <v>52</v>
       </c>
       <c r="B518" s="3">
-        <v>48852</v>
+        <v>46111</v>
       </c>
       <c r="C518" s="2">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D518" s="2">
-        <v>0.88</v>
+        <v>3.5</v>
       </c>
       <c r="E518" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G518" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B519" s="3">
-        <v>46081</v>
+        <v>46295</v>
       </c>
       <c r="C519" s="2">
         <v>100</v>
       </c>
       <c r="D519" s="2">
-        <v>1.51</v>
+        <v>3.5</v>
       </c>
       <c r="E519" s="2">
         <v>0</v>
@@ -13013,39 +13058,39 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B520" s="3">
-        <v>46170</v>
+        <v>46476</v>
       </c>
       <c r="C520" s="2">
         <v>100</v>
       </c>
       <c r="D520" s="2">
-        <v>1.46</v>
+        <v>3.5</v>
       </c>
       <c r="E520" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F520" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G520" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B521" s="3">
-        <v>46092</v>
+        <v>46660</v>
       </c>
       <c r="C521" s="2">
         <v>100</v>
       </c>
       <c r="D521" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E521" s="2">
         <v>0</v>
@@ -13059,16 +13104,16 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B522" s="3">
-        <v>46276</v>
+        <v>46842</v>
       </c>
       <c r="C522" s="2">
         <v>100</v>
       </c>
       <c r="D522" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E522" s="2">
         <v>0</v>
@@ -13082,16 +13127,16 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B523" s="3">
-        <v>46457</v>
+        <v>47026</v>
       </c>
       <c r="C523" s="2">
         <v>100</v>
       </c>
       <c r="D523" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E523" s="2">
         <v>0</v>
@@ -13105,16 +13150,16 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B524" s="3">
-        <v>46641</v>
+        <v>47207</v>
       </c>
       <c r="C524" s="2">
         <v>100</v>
       </c>
       <c r="D524" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E524" s="2">
         <v>0</v>
@@ -13128,16 +13173,16 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B525" s="3">
-        <v>46823</v>
+        <v>47391</v>
       </c>
       <c r="C525" s="2">
         <v>100</v>
       </c>
       <c r="D525" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E525" s="2">
         <v>0</v>
@@ -13151,16 +13196,16 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B526" s="3">
-        <v>47007</v>
+        <v>47572</v>
       </c>
       <c r="C526" s="2">
         <v>100</v>
       </c>
       <c r="D526" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E526" s="2">
         <v>0</v>
@@ -13174,143 +13219,492 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B527" s="3">
-        <v>47188</v>
+        <v>47756</v>
       </c>
       <c r="C527" s="2">
         <v>100</v>
       </c>
       <c r="D527" s="2">
-        <v>4.38</v>
+        <v>3.5</v>
       </c>
       <c r="E527" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G527" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B528" s="3">
-        <v>47372</v>
+        <v>47937</v>
       </c>
       <c r="C528" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D528" s="2">
-        <v>4.38</v>
+        <v>2.62</v>
       </c>
       <c r="E528" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G528" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B529" s="3">
-        <v>47553</v>
+        <v>48121</v>
       </c>
       <c r="C529" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D529" s="2">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="E529" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G529" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B530" s="3">
-        <v>47737</v>
+        <v>48303</v>
       </c>
       <c r="C530" s="2">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D530" s="2">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="E530" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G530" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B531" s="3">
-        <v>47918</v>
+        <v>48487</v>
       </c>
       <c r="C531" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D531" s="2">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="E531" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G531" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B532" s="3">
+        <v>48668</v>
+      </c>
+      <c r="C532" s="2">
+        <v>25</v>
+      </c>
+      <c r="D532" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="E532" s="2">
+        <v>0</v>
+      </c>
+      <c r="F532" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G532" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A533" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B533" s="3">
+        <v>48852</v>
+      </c>
+      <c r="C533" s="2">
+        <v>25</v>
+      </c>
+      <c r="D533" s="2">
+        <v>0.88</v>
+      </c>
+      <c r="E533" s="2">
+        <v>25</v>
+      </c>
+      <c r="F533" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G533" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A534" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B534" s="3">
+        <v>46081</v>
+      </c>
+      <c r="C534" s="2">
+        <v>100</v>
+      </c>
+      <c r="D534" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="E534" s="2">
+        <v>0</v>
+      </c>
+      <c r="F534" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G534" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A535" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B535" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C535" s="2">
+        <v>100</v>
+      </c>
+      <c r="D535" s="2">
+        <v>1.46</v>
+      </c>
+      <c r="E535" s="2">
+        <v>100</v>
+      </c>
+      <c r="F535" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G535" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A536" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B532" s="3">
+      <c r="B536" s="3">
+        <v>46092</v>
+      </c>
+      <c r="C536" s="2">
+        <v>100</v>
+      </c>
+      <c r="D536" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E536" s="2">
+        <v>0</v>
+      </c>
+      <c r="F536" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G536" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A537" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B537" s="3">
+        <v>46276</v>
+      </c>
+      <c r="C537" s="2">
+        <v>100</v>
+      </c>
+      <c r="D537" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E537" s="2">
+        <v>0</v>
+      </c>
+      <c r="F537" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G537" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A538" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B538" s="3">
+        <v>46457</v>
+      </c>
+      <c r="C538" s="2">
+        <v>100</v>
+      </c>
+      <c r="D538" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E538" s="2">
+        <v>0</v>
+      </c>
+      <c r="F538" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G538" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A539" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B539" s="3">
+        <v>46641</v>
+      </c>
+      <c r="C539" s="2">
+        <v>100</v>
+      </c>
+      <c r="D539" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E539" s="2">
+        <v>0</v>
+      </c>
+      <c r="F539" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G539" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A540" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B540" s="3">
+        <v>46823</v>
+      </c>
+      <c r="C540" s="2">
+        <v>100</v>
+      </c>
+      <c r="D540" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E540" s="2">
+        <v>0</v>
+      </c>
+      <c r="F540" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G540" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A541" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B541" s="3">
+        <v>47007</v>
+      </c>
+      <c r="C541" s="2">
+        <v>100</v>
+      </c>
+      <c r="D541" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E541" s="2">
+        <v>0</v>
+      </c>
+      <c r="F541" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G541" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A542" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B542" s="3">
+        <v>47188</v>
+      </c>
+      <c r="C542" s="2">
+        <v>100</v>
+      </c>
+      <c r="D542" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E542" s="2">
+        <v>0</v>
+      </c>
+      <c r="F542" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A543" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B543" s="3">
+        <v>47372</v>
+      </c>
+      <c r="C543" s="2">
+        <v>100</v>
+      </c>
+      <c r="D543" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="E543" s="2">
+        <v>20</v>
+      </c>
+      <c r="F543" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G543" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A544" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B544" s="3">
+        <v>47553</v>
+      </c>
+      <c r="C544" s="2">
+        <v>80</v>
+      </c>
+      <c r="D544" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="E544" s="2">
+        <v>0</v>
+      </c>
+      <c r="F544" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G544" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A545" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B545" s="3">
+        <v>47737</v>
+      </c>
+      <c r="C545" s="2">
+        <v>80</v>
+      </c>
+      <c r="D545" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="E545" s="2">
+        <v>20</v>
+      </c>
+      <c r="F545" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G545" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A546" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B546" s="3">
+        <v>47918</v>
+      </c>
+      <c r="C546" s="2">
+        <v>60</v>
+      </c>
+      <c r="D546" s="2">
+        <v>2.62</v>
+      </c>
+      <c r="E546" s="2">
+        <v>0</v>
+      </c>
+      <c r="F546" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G546" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A547" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B547" s="3">
         <v>48102</v>
       </c>
-      <c r="C532" s="2">
+      <c r="C547" s="2">
         <v>60</v>
       </c>
-      <c r="D532" s="2">
+      <c r="D547" s="2">
         <v>2.62</v>
       </c>
-      <c r="E532" s="2">
+      <c r="E547" s="2">
         <v>60</v>
       </c>
-      <c r="F532" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G532" s="1" t="s">
+      <c r="F547" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G547" s="1" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G547">
+    <sortCondition ref="A2:A547"/>
+    <sortCondition ref="B2:B547"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/bonos_flujos.xlsx
+++ b/data/bonos_flujos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4288AF5C-3856-4CB5-81C2-6056605CED08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A850B608-B095-4178-B2B0-4C0A18D59CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80832C3D-9255-40D8-8540-27B2F4252002}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{80832C3D-9255-40D8-8540-27B2F4252002}"/>
   </bookViews>
   <sheets>
     <sheet name="bonos_flujos" sheetId="1" r:id="rId1"/>
@@ -94,16 +94,10 @@
     <t>BPY6D</t>
   </si>
   <si>
-    <t>CS38O</t>
-  </si>
-  <si>
     <t>CUAP</t>
   </si>
   <si>
     <t>DICP</t>
-  </si>
-  <si>
-    <t>DNC3O</t>
   </si>
   <si>
     <t>GD29D</t>
@@ -124,67 +118,16 @@
     <t>GD46D</t>
   </si>
   <si>
-    <t>IRCNO</t>
-  </si>
-  <si>
-    <t>IRCOO</t>
-  </si>
-  <si>
-    <t>LMS9O</t>
-  </si>
-  <si>
-    <t>MTCGO</t>
-  </si>
-  <si>
     <t>PAP0</t>
   </si>
   <si>
     <t>PARP</t>
   </si>
   <si>
-    <t>PN35O</t>
-  </si>
-  <si>
-    <t>PN36O</t>
-  </si>
-  <si>
-    <t>PN37O</t>
-  </si>
-  <si>
-    <t>TLC1O</t>
-  </si>
-  <si>
-    <t>TLCMO</t>
-  </si>
-  <si>
     <t>TX26</t>
   </si>
   <si>
     <t>ARS CER</t>
-  </si>
-  <si>
-    <t>VSCRO</t>
-  </si>
-  <si>
-    <t>VSCTO</t>
-  </si>
-  <si>
-    <t>YFCJO</t>
-  </si>
-  <si>
-    <t>YM34O</t>
-  </si>
-  <si>
-    <t>YMCIO</t>
-  </si>
-  <si>
-    <t>YMCJO</t>
-  </si>
-  <si>
-    <t>YMCVO</t>
-  </si>
-  <si>
-    <t>YMCXO</t>
   </si>
   <si>
     <t>S27F6</t>
@@ -230,6 +173,63 @@
   </si>
   <si>
     <t>T30J7</t>
+  </si>
+  <si>
+    <t>CS38D</t>
+  </si>
+  <si>
+    <t>DNC3D</t>
+  </si>
+  <si>
+    <t>IRCND</t>
+  </si>
+  <si>
+    <t>IRCOD</t>
+  </si>
+  <si>
+    <t>LMS9D</t>
+  </si>
+  <si>
+    <t>MTCGD</t>
+  </si>
+  <si>
+    <t>PN35D</t>
+  </si>
+  <si>
+    <t>PN36D</t>
+  </si>
+  <si>
+    <t>PN37D</t>
+  </si>
+  <si>
+    <t>TLC1D</t>
+  </si>
+  <si>
+    <t>TLCMD</t>
+  </si>
+  <si>
+    <t>VSCRD</t>
+  </si>
+  <si>
+    <t>VSCTD</t>
+  </si>
+  <si>
+    <t>YFCJD</t>
+  </si>
+  <si>
+    <t>YM34D</t>
+  </si>
+  <si>
+    <t>YMCID</t>
+  </si>
+  <si>
+    <t>YMCJD</t>
+  </si>
+  <si>
+    <t>YMCVD</t>
+  </si>
+  <si>
+    <t>YMCXD</t>
   </si>
 </sst>
 </file>
@@ -4180,7 +4180,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B134" s="3">
         <v>46084</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B135" s="3">
         <v>46203</v>
@@ -4226,7 +4226,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B136" s="3">
         <v>46387</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B137" s="3">
         <v>46568</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B138" s="3">
         <v>46752</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B139" s="3">
         <v>46934</v>
@@ -4318,7 +4318,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B140" s="3">
         <v>47118</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B141" s="3">
         <v>47299</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B142" s="3">
         <v>47483</v>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B143" s="3">
         <v>47664</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B144" s="3">
         <v>47848</v>
@@ -4433,7 +4433,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B145" s="3">
         <v>48029</v>
@@ -4456,7 +4456,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B146" s="3">
         <v>48213</v>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B147" s="3">
         <v>48395</v>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B148" s="3">
         <v>48579</v>
@@ -4525,7 +4525,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B149" s="3">
         <v>48760</v>
@@ -4548,7 +4548,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B150" s="3">
         <v>48944</v>
@@ -4571,7 +4571,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B151" s="3">
         <v>49125</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B152" s="3">
         <v>49309</v>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B153" s="3">
         <v>49490</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B154" s="3">
         <v>49674</v>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B155" s="3">
         <v>49856</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B156" s="3">
         <v>50040</v>
@@ -4709,7 +4709,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B157" s="3">
         <v>50221</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B158" s="3">
         <v>50405</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B159" s="3">
         <v>50586</v>
@@ -4778,7 +4778,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B160" s="3">
         <v>50770</v>
@@ -4801,7 +4801,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B161" s="3">
         <v>50951</v>
@@ -4824,7 +4824,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B162" s="3">
         <v>51135</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B163" s="3">
         <v>51317</v>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B164" s="3">
         <v>51501</v>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B165" s="3">
         <v>51682</v>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B166" s="3">
         <v>51866</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B167" s="3">
         <v>52047</v>
@@ -4962,7 +4962,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B168" s="3">
         <v>52231</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B169" s="3">
         <v>52412</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B170" s="3">
         <v>52596</v>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B171" s="3">
         <v>52778</v>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B172" s="3">
         <v>52962</v>
@@ -5077,7 +5077,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B173" s="3">
         <v>53143</v>
@@ -5100,7 +5100,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B174" s="3">
         <v>53327</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B175" s="3">
         <v>46203</v>
@@ -5146,7 +5146,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B176" s="3">
         <v>46387</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B177" s="3">
         <v>46568</v>
@@ -5192,7 +5192,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B178" s="3">
         <v>46752</v>
@@ -5215,7 +5215,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B179" s="3">
         <v>46934</v>
@@ -5238,7 +5238,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B180" s="3">
         <v>47118</v>
@@ -5261,7 +5261,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B181" s="3">
         <v>47299</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B182" s="3">
         <v>47483</v>
@@ -5307,7 +5307,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B183" s="3">
         <v>47664</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B184" s="3">
         <v>47848</v>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B185" s="3">
         <v>48029</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B186" s="3">
         <v>48213</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B187" s="3">
         <v>48395</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B188" s="3">
         <v>48579</v>
@@ -5445,7 +5445,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B189" s="3">
         <v>48760</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B190" s="3">
         <v>48944</v>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B191" s="3">
         <v>46164</v>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B192" s="3">
         <v>46348</v>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B193" s="3">
         <v>46212</v>
@@ -5560,7 +5560,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B194" s="3">
         <v>46396</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B195" s="3">
         <v>46577</v>
@@ -5606,7 +5606,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B196" s="3">
         <v>46761</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B197" s="3">
         <v>46943</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B198" s="3">
         <v>47127</v>
@@ -5675,7 +5675,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B199" s="3">
         <v>47308</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B200" s="3">
         <v>46212</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B201" s="3">
         <v>46396</v>
@@ -5744,7 +5744,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B202" s="3">
         <v>46577</v>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B203" s="3">
         <v>46761</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B204" s="3">
         <v>46943</v>
@@ -5813,7 +5813,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B205" s="3">
         <v>47127</v>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B206" s="3">
         <v>47308</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B207" s="3">
         <v>47492</v>
@@ -5882,7 +5882,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B208" s="3">
         <v>47673</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B209" s="3">
         <v>46212</v>
@@ -5928,7 +5928,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B210" s="3">
         <v>46396</v>
@@ -5951,7 +5951,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B211" s="3">
         <v>46577</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B212" s="3">
         <v>46761</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B213" s="3">
         <v>46943</v>
@@ -6020,7 +6020,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B214" s="3">
         <v>47127</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B215" s="3">
         <v>47308</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B216" s="3">
         <v>47492</v>
@@ -6089,7 +6089,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B217" s="3">
         <v>47673</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B218" s="3">
         <v>47857</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B219" s="3">
         <v>48038</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B220" s="3">
         <v>48222</v>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B221" s="3">
         <v>48404</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B222" s="3">
         <v>48588</v>
@@ -6227,7 +6227,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B223" s="3">
         <v>48769</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B224" s="3">
         <v>48953</v>
@@ -6273,7 +6273,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B225" s="3">
         <v>49134</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B226" s="3">
         <v>49318</v>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B227" s="3">
         <v>49499</v>
@@ -6342,7 +6342,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B228" s="3">
         <v>46212</v>
@@ -6365,7 +6365,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B229" s="3">
         <v>46396</v>
@@ -6388,7 +6388,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B230" s="3">
         <v>46577</v>
@@ -6411,7 +6411,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B231" s="3">
         <v>46761</v>
@@ -6434,7 +6434,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B232" s="3">
         <v>46943</v>
@@ -6457,7 +6457,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B233" s="3">
         <v>47127</v>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B234" s="3">
         <v>47308</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B235" s="3">
         <v>47492</v>
@@ -6526,7 +6526,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B236" s="3">
         <v>47673</v>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B237" s="3">
         <v>47857</v>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B238" s="3">
         <v>48038</v>
@@ -6595,7 +6595,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B239" s="3">
         <v>48222</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B240" s="3">
         <v>48404</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B241" s="3">
         <v>48588</v>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B242" s="3">
         <v>48769</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B243" s="3">
         <v>48953</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B244" s="3">
         <v>49134</v>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B245" s="3">
         <v>49318</v>
@@ -6756,7 +6756,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B246" s="3">
         <v>49499</v>
@@ -6779,7 +6779,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B247" s="3">
         <v>49683</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B248" s="3">
         <v>49865</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B249" s="3">
         <v>50049</v>
@@ -6848,7 +6848,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B250" s="3">
         <v>50230</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B251" s="3">
         <v>50414</v>
@@ -6894,7 +6894,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B252" s="3">
         <v>46212</v>
@@ -6917,7 +6917,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B253" s="3">
         <v>46396</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B254" s="3">
         <v>46577</v>
@@ -6963,7 +6963,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B255" s="3">
         <v>46761</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B256" s="3">
         <v>46943</v>
@@ -7009,7 +7009,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B257" s="3">
         <v>47127</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B258" s="3">
         <v>47308</v>
@@ -7055,7 +7055,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B259" s="3">
         <v>47492</v>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B260" s="3">
         <v>47673</v>
@@ -7101,7 +7101,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B261" s="3">
         <v>47857</v>
@@ -7124,7 +7124,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B262" s="3">
         <v>48038</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B263" s="3">
         <v>48222</v>
@@ -7170,7 +7170,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B264" s="3">
         <v>48404</v>
@@ -7193,7 +7193,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B265" s="3">
         <v>48588</v>
@@ -7216,7 +7216,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B266" s="3">
         <v>48769</v>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B267" s="3">
         <v>48953</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B268" s="3">
         <v>49134</v>
@@ -7285,7 +7285,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B269" s="3">
         <v>49318</v>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B270" s="3">
         <v>49499</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B271" s="3">
         <v>49683</v>
@@ -7354,7 +7354,7 @@
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B272" s="3">
         <v>49865</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B273" s="3">
         <v>50049</v>
@@ -7400,7 +7400,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B274" s="3">
         <v>50230</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B275" s="3">
         <v>50414</v>
@@ -7446,7 +7446,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B276" s="3">
         <v>50595</v>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B277" s="3">
         <v>50779</v>
@@ -7492,7 +7492,7 @@
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B278" s="3">
         <v>50960</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B279" s="3">
         <v>51144</v>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B280" s="3">
         <v>51326</v>
@@ -7561,7 +7561,7 @@
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B281" s="3">
         <v>51510</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B282" s="3">
         <v>51691</v>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B283" s="3">
         <v>46212</v>
@@ -7630,7 +7630,7 @@
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B284" s="3">
         <v>46396</v>
@@ -7653,7 +7653,7 @@
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B285" s="3">
         <v>46577</v>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B286" s="3">
         <v>46761</v>
@@ -7699,7 +7699,7 @@
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B287" s="3">
         <v>46943</v>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B288" s="3">
         <v>47127</v>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B289" s="3">
         <v>47308</v>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B290" s="3">
         <v>47492</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B291" s="3">
         <v>47673</v>
@@ -7814,7 +7814,7 @@
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B292" s="3">
         <v>47857</v>
@@ -7837,7 +7837,7 @@
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B293" s="3">
         <v>48038</v>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B294" s="3">
         <v>48222</v>
@@ -7883,7 +7883,7 @@
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B295" s="3">
         <v>48404</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B296" s="3">
         <v>48588</v>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B297" s="3">
         <v>48769</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B298" s="3">
         <v>48953</v>
@@ -7975,7 +7975,7 @@
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B299" s="3">
         <v>49134</v>
@@ -7998,7 +7998,7 @@
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B300" s="3">
         <v>49318</v>
@@ -8021,7 +8021,7 @@
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B301" s="3">
         <v>49499</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B302" s="3">
         <v>49683</v>
@@ -8067,7 +8067,7 @@
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B303" s="3">
         <v>49865</v>
@@ -8090,7 +8090,7 @@
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B304" s="3">
         <v>50049</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B305" s="3">
         <v>50230</v>
@@ -8136,7 +8136,7 @@
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B306" s="3">
         <v>50414</v>
@@ -8159,7 +8159,7 @@
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B307" s="3">
         <v>50595</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B308" s="3">
         <v>50779</v>
@@ -8205,7 +8205,7 @@
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B309" s="3">
         <v>50960</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B310" s="3">
         <v>51144</v>
@@ -8251,7 +8251,7 @@
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B311" s="3">
         <v>51326</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B312" s="3">
         <v>51510</v>
@@ -8297,7 +8297,7 @@
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B313" s="3">
         <v>51691</v>
@@ -8320,7 +8320,7 @@
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B314" s="3">
         <v>51875</v>
@@ -8343,7 +8343,7 @@
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B315" s="3">
         <v>52056</v>
@@ -8366,7 +8366,7 @@
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B316" s="3">
         <v>52240</v>
@@ -8389,7 +8389,7 @@
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B317" s="3">
         <v>52421</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B318" s="3">
         <v>52605</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B319" s="3">
         <v>52787</v>
@@ -8458,7 +8458,7 @@
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B320" s="3">
         <v>52971</v>
@@ -8481,7 +8481,7 @@
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B321" s="3">
         <v>53152</v>
@@ -8504,7 +8504,7 @@
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B322" s="3">
         <v>53336</v>
@@ -8527,7 +8527,7 @@
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B323" s="3">
         <v>53517</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B324" s="3">
         <v>46225</v>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B325" s="3">
         <v>46409</v>
@@ -8596,7 +8596,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B326" s="3">
         <v>46590</v>
@@ -8619,7 +8619,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B327" s="3">
         <v>46682</v>
@@ -8642,7 +8642,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B328" s="3">
         <v>46226</v>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B329" s="3">
         <v>46410</v>
@@ -8688,7 +8688,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B330" s="3">
         <v>46591</v>
@@ -8711,7 +8711,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B331" s="3">
         <v>46775</v>
@@ -8734,7 +8734,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B332" s="3">
         <v>46957</v>
@@ -8757,7 +8757,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B333" s="3">
         <v>47141</v>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B334" s="3">
         <v>47322</v>
@@ -8803,7 +8803,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B335" s="3">
         <v>47414</v>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B336" s="3">
         <v>46094</v>
@@ -8849,7 +8849,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B337" s="3">
         <v>46186</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B338" s="3">
         <v>46111</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B339" s="3">
         <v>46203</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B340" s="3">
         <v>46112</v>
@@ -8941,7 +8941,7 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B341" s="3">
         <v>46295</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B342" s="3">
         <v>46477</v>
@@ -8987,7 +8987,7 @@
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B343" s="3">
         <v>46660</v>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B344" s="3">
         <v>46843</v>
@@ -9033,7 +9033,7 @@
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B345" s="3">
         <v>47026</v>
@@ -9056,7 +9056,7 @@
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B346" s="3">
         <v>47208</v>
@@ -9079,7 +9079,7 @@
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B347" s="3">
         <v>47391</v>
@@ -9102,7 +9102,7 @@
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B348" s="3">
         <v>47573</v>
@@ -9125,7 +9125,7 @@
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B349" s="3">
         <v>47756</v>
@@ -9148,7 +9148,7 @@
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B350" s="3">
         <v>47938</v>
@@ -9171,7 +9171,7 @@
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B351" s="3">
         <v>48121</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B352" s="3">
         <v>48304</v>
@@ -9217,7 +9217,7 @@
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B353" s="3">
         <v>48487</v>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B354" s="3">
         <v>48669</v>
@@ -9263,7 +9263,7 @@
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B355" s="3">
         <v>48852</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B356" s="3">
         <v>49034</v>
@@ -9309,7 +9309,7 @@
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B357" s="3">
         <v>49217</v>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B358" s="3">
         <v>49399</v>
@@ -9355,7 +9355,7 @@
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B359" s="3">
         <v>49582</v>
@@ -9378,7 +9378,7 @@
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B360" s="3">
         <v>49765</v>
@@ -9401,7 +9401,7 @@
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B361" s="3">
         <v>49948</v>
@@ -9424,7 +9424,7 @@
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B362" s="3">
         <v>50130</v>
@@ -9447,7 +9447,7 @@
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B363" s="3">
         <v>50313</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B364" s="3">
         <v>50495</v>
@@ -9493,7 +9493,7 @@
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B365" s="3">
         <v>50678</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B366" s="3">
         <v>50770</v>
@@ -9539,7 +9539,7 @@
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B367" s="3">
         <v>46112</v>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B368" s="3">
         <v>46295</v>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B369" s="3">
         <v>46477</v>
@@ -9608,7 +9608,7 @@
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B370" s="3">
         <v>46660</v>
@@ -9631,7 +9631,7 @@
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B371" s="3">
         <v>46843</v>
@@ -9654,7 +9654,7 @@
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B372" s="3">
         <v>47026</v>
@@ -9677,7 +9677,7 @@
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B373" s="3">
         <v>47208</v>
@@ -9700,7 +9700,7 @@
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B374" s="3">
         <v>47391</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B375" s="3">
         <v>47573</v>
@@ -9746,7 +9746,7 @@
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B376" s="3">
         <v>47756</v>
@@ -9769,7 +9769,7 @@
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B377" s="3">
         <v>47938</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B378" s="3">
         <v>48121</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B379" s="3">
         <v>48304</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B380" s="3">
         <v>48487</v>
@@ -9861,7 +9861,7 @@
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B381" s="3">
         <v>48669</v>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B382" s="3">
         <v>48852</v>
@@ -9907,7 +9907,7 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B383" s="3">
         <v>49034</v>
@@ -9930,7 +9930,7 @@
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B384" s="3">
         <v>49217</v>
@@ -9953,7 +9953,7 @@
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B385" s="3">
         <v>49399</v>
@@ -9976,7 +9976,7 @@
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B386" s="3">
         <v>49582</v>
@@ -9999,7 +9999,7 @@
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B387" s="3">
         <v>49765</v>
@@ -10022,7 +10022,7 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B388" s="3">
         <v>49948</v>
@@ -10045,7 +10045,7 @@
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B389" s="3">
         <v>50130</v>
@@ -10068,7 +10068,7 @@
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B390" s="3">
         <v>50313</v>
@@ -10091,7 +10091,7 @@
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B391" s="3">
         <v>50495</v>
@@ -10114,7 +10114,7 @@
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B392" s="3">
         <v>50678</v>
@@ -10137,7 +10137,7 @@
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B393" s="3">
         <v>50770</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B394" s="3">
         <v>46108</v>
@@ -10183,7 +10183,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B395" s="3">
         <v>46292</v>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B396" s="3">
         <v>46473</v>
@@ -10229,7 +10229,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B397" s="3">
         <v>46657</v>
@@ -10252,7 +10252,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B398" s="3">
         <v>46839</v>
@@ -10275,7 +10275,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B399" s="3">
         <v>47023</v>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B400" s="3">
         <v>47204</v>
@@ -10321,7 +10321,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B401" s="3">
         <v>47388</v>
@@ -10344,7 +10344,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B402" s="3">
         <v>46155</v>
@@ -10367,7 +10367,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B403" s="3">
         <v>46339</v>
@@ -10390,7 +10390,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B404" s="3">
         <v>46520</v>
@@ -10413,7 +10413,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B405" s="3">
         <v>46704</v>
@@ -10436,7 +10436,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B406" s="3">
         <v>46886</v>
@@ -10459,7 +10459,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B407" s="3">
         <v>47070</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B408" s="3">
         <v>47251</v>
@@ -10505,7 +10505,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B409" s="3">
         <v>47435</v>
@@ -10528,7 +10528,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B410" s="3">
         <v>47616</v>
@@ -10551,7 +10551,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B411" s="3">
         <v>47800</v>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B412" s="3">
         <v>47981</v>
@@ -10597,7 +10597,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B413" s="3">
         <v>48165</v>
@@ -10620,7 +10620,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B414" s="3">
         <v>46155</v>
@@ -10643,7 +10643,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B415" s="3">
         <v>46339</v>
@@ -10666,7 +10666,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B416" s="3">
         <v>46520</v>
@@ -10689,7 +10689,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B417" s="3">
         <v>46704</v>
@@ -10712,7 +10712,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B418" s="3">
         <v>46886</v>
@@ -10735,7 +10735,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="B419" s="3">
         <v>47070</v>
@@ -10758,7 +10758,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B420" s="3">
         <v>46097</v>
@@ -10781,7 +10781,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B421" s="3">
         <v>46129</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B422" s="3">
         <v>46080</v>
@@ -10827,7 +10827,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B423" s="3">
         <v>46171</v>
@@ -10850,7 +10850,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B424" s="3">
         <v>46142</v>
@@ -10873,7 +10873,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B425" s="3">
         <v>46356</v>
@@ -10896,7 +10896,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B426" s="3">
         <v>46325</v>
@@ -10919,7 +10919,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B427" s="3">
         <v>46265</v>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B428" s="3">
         <v>46234</v>
@@ -10965,7 +10965,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B429" s="3">
         <v>46066</v>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B430" s="3">
         <v>46402</v>
@@ -11011,7 +11011,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B431" s="3">
         <v>46507</v>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B432" s="3">
         <v>46203</v>
@@ -11057,7 +11057,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B433" s="3">
         <v>46568</v>
@@ -11080,7 +11080,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B434" s="3">
         <v>46538</v>
@@ -11103,7 +11103,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B435" s="3">
         <v>46221</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B436" s="3">
         <v>46221</v>
@@ -11149,7 +11149,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B437" s="3">
         <v>46405</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B438" s="3">
         <v>46586</v>
@@ -11195,7 +11195,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B439" s="3">
         <v>46770</v>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B440" s="3">
         <v>46952</v>
@@ -11241,7 +11241,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B441" s="3">
         <v>47136</v>
@@ -11264,7 +11264,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B442" s="3">
         <v>47317</v>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B443" s="3">
         <v>47501</v>
@@ -11310,7 +11310,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B444" s="3">
         <v>47682</v>
@@ -11333,7 +11333,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B445" s="3">
         <v>47866</v>
@@ -11356,7 +11356,7 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B446" s="3">
         <v>48047</v>
@@ -11379,7 +11379,7 @@
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B447" s="3">
         <v>46151</v>
@@ -11394,7 +11394,7 @@
         <v>20</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>16</v>
@@ -11402,7 +11402,7 @@
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B448" s="3">
         <v>46335</v>
@@ -11417,7 +11417,7 @@
         <v>20</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>16</v>
@@ -11425,7 +11425,7 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B449" s="3">
         <v>46122</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B450" s="3">
         <v>46305</v>
@@ -11471,7 +11471,7 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B451" s="3">
         <v>46487</v>
@@ -11494,7 +11494,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B452" s="3">
         <v>46670</v>
@@ -11517,7 +11517,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B453" s="3">
         <v>46853</v>
@@ -11540,7 +11540,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B454" s="3">
         <v>47036</v>
@@ -11563,7 +11563,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B455" s="3">
         <v>47218</v>
@@ -11586,7 +11586,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B456" s="3">
         <v>47401</v>
@@ -11609,7 +11609,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B457" s="3">
         <v>47583</v>
@@ -11632,7 +11632,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B458" s="3">
         <v>47766</v>
@@ -11655,7 +11655,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B459" s="3">
         <v>47948</v>
@@ -11678,7 +11678,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B460" s="3">
         <v>48131</v>
@@ -11701,7 +11701,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B461" s="3">
         <v>46183</v>
@@ -11724,7 +11724,7 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B462" s="3">
         <v>46366</v>
@@ -11747,7 +11747,7 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B463" s="3">
         <v>46548</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B464" s="3">
         <v>46731</v>
@@ -11793,7 +11793,7 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B465" s="3">
         <v>46914</v>
@@ -11816,7 +11816,7 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B466" s="3">
         <v>47097</v>
@@ -11839,7 +11839,7 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B467" s="3">
         <v>47279</v>
@@ -11862,7 +11862,7 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B468" s="3">
         <v>47462</v>
@@ -11885,7 +11885,7 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B469" s="3">
         <v>47644</v>
@@ -11908,7 +11908,7 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B470" s="3">
         <v>47827</v>
@@ -11931,7 +11931,7 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B471" s="3">
         <v>48009</v>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B472" s="3">
         <v>48192</v>
@@ -11977,7 +11977,7 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B473" s="3">
         <v>48375</v>
@@ -12000,7 +12000,7 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B474" s="3">
         <v>48558</v>
@@ -12023,7 +12023,7 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B475" s="3">
         <v>48740</v>
@@ -12046,7 +12046,7 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B476" s="3">
         <v>48923</v>
@@ -12069,7 +12069,7 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B477" s="3">
         <v>49105</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B478" s="3">
         <v>49288</v>
@@ -12115,7 +12115,7 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B479" s="3">
         <v>49470</v>
@@ -12138,7 +12138,7 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B480" s="3">
         <v>49653</v>
@@ -12161,7 +12161,7 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B481" s="3">
         <v>46128</v>
@@ -12184,7 +12184,7 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B482" s="3">
         <v>46311</v>
@@ -12207,7 +12207,7 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B483" s="3">
         <v>46493</v>
@@ -12230,7 +12230,7 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B484" s="3">
         <v>46676</v>
@@ -12253,7 +12253,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B485" s="3">
         <v>46859</v>
@@ -12276,7 +12276,7 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B486" s="3">
         <v>47042</v>
@@ -12299,7 +12299,7 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B487" s="3">
         <v>47224</v>
@@ -12322,7 +12322,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B488" s="3">
         <v>47407</v>
@@ -12345,7 +12345,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B489" s="3">
         <v>47589</v>
@@ -12368,7 +12368,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B490" s="3">
         <v>47772</v>
@@ -12391,7 +12391,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B491" s="3">
         <v>47954</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B492" s="3">
         <v>48137</v>
@@ -12437,7 +12437,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B493" s="3">
         <v>48320</v>
@@ -12460,7 +12460,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B494" s="3">
         <v>48503</v>
@@ -12483,7 +12483,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B495" s="3">
         <v>46220</v>
@@ -12506,7 +12506,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B496" s="3">
         <v>46404</v>
@@ -12529,7 +12529,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B497" s="3">
         <v>46585</v>
@@ -12552,7 +12552,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B498" s="3">
         <v>46769</v>
@@ -12575,7 +12575,7 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B499" s="3">
         <v>46951</v>
@@ -12598,7 +12598,7 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B500" s="3">
         <v>47135</v>
@@ -12621,7 +12621,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B501" s="3">
         <v>47316</v>
@@ -12644,7 +12644,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B502" s="3">
         <v>47500</v>
@@ -12667,7 +12667,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B503" s="3">
         <v>47681</v>
@@ -12690,7 +12690,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B504" s="3">
         <v>47865</v>
@@ -12713,7 +12713,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B505" s="3">
         <v>48046</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B506" s="3">
         <v>48230</v>
@@ -12759,7 +12759,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B507" s="3">
         <v>48412</v>
@@ -12782,7 +12782,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B508" s="3">
         <v>48596</v>
@@ -12805,7 +12805,7 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B509" s="3">
         <v>48777</v>
@@ -12828,7 +12828,7 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B510" s="3">
         <v>48961</v>
@@ -12851,7 +12851,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B511" s="3">
         <v>46203</v>
@@ -12874,7 +12874,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B512" s="3">
         <v>46386</v>
@@ -12897,7 +12897,7 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B513" s="3">
         <v>46568</v>
@@ -12920,7 +12920,7 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B514" s="3">
         <v>46751</v>
@@ -12943,7 +12943,7 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B515" s="3">
         <v>46934</v>
@@ -12966,7 +12966,7 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B516" s="3">
         <v>47117</v>
@@ -12989,7 +12989,7 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B517" s="3">
         <v>47299</v>
@@ -13012,7 +13012,7 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B518" s="3">
         <v>46111</v>
@@ -13035,7 +13035,7 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B519" s="3">
         <v>46295</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B520" s="3">
         <v>46476</v>
@@ -13081,7 +13081,7 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B521" s="3">
         <v>46660</v>
@@ -13104,7 +13104,7 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B522" s="3">
         <v>46842</v>
@@ -13127,7 +13127,7 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B523" s="3">
         <v>47026</v>
@@ -13150,7 +13150,7 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B524" s="3">
         <v>47207</v>
@@ -13173,7 +13173,7 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B525" s="3">
         <v>47391</v>
@@ -13196,7 +13196,7 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B526" s="3">
         <v>47572</v>
@@ -13219,7 +13219,7 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B527" s="3">
         <v>47756</v>
@@ -13242,7 +13242,7 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B528" s="3">
         <v>47937</v>
@@ -13265,7 +13265,7 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B529" s="3">
         <v>48121</v>
@@ -13288,7 +13288,7 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B530" s="3">
         <v>48303</v>
@@ -13311,7 +13311,7 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B531" s="3">
         <v>48487</v>
@@ -13334,7 +13334,7 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B532" s="3">
         <v>48668</v>
@@ -13357,7 +13357,7 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B533" s="3">
         <v>48852</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B534" s="3">
         <v>46081</v>
@@ -13403,7 +13403,7 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B535" s="3">
         <v>46170</v>
@@ -13426,7 +13426,7 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B536" s="3">
         <v>46092</v>
@@ -13449,7 +13449,7 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B537" s="3">
         <v>46276</v>
@@ -13472,7 +13472,7 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B538" s="3">
         <v>46457</v>
@@ -13495,7 +13495,7 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B539" s="3">
         <v>46641</v>
@@ -13518,7 +13518,7 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B540" s="3">
         <v>46823</v>
@@ -13541,7 +13541,7 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B541" s="3">
         <v>47007</v>
@@ -13564,7 +13564,7 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B542" s="3">
         <v>47188</v>
@@ -13587,7 +13587,7 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B543" s="3">
         <v>47372</v>
@@ -13610,7 +13610,7 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B544" s="3">
         <v>47553</v>
@@ -13633,7 +13633,7 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B545" s="3">
         <v>47737</v>
@@ -13656,7 +13656,7 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B546" s="3">
         <v>47918</v>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B547" s="3">
         <v>48102</v>

--- a/data/bonos_flujos.xlsx
+++ b/data/bonos_flujos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomas\SPR-BS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A850B608-B095-4178-B2B0-4C0A18D59CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D4F66E-36B1-48F5-812B-20ECF386EEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{80832C3D-9255-40D8-8540-27B2F4252002}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80832C3D-9255-40D8-8540-27B2F4252002}"/>
   </bookViews>
   <sheets>
     <sheet name="bonos_flujos" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="69">
   <si>
     <t>codigo</t>
   </si>
@@ -125,9 +125,6 @@
   </si>
   <si>
     <t>TX26</t>
-  </si>
-  <si>
-    <t>ARS CER</t>
   </si>
   <si>
     <t>S27F6</t>
@@ -4180,7 +4177,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B134" s="3">
         <v>46084</v>
@@ -5491,7 +5488,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B191" s="3">
         <v>46164</v>
@@ -5514,7 +5511,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B192" s="3">
         <v>46348</v>
@@ -8550,7 +8547,7 @@
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B324" s="3">
         <v>46225</v>
@@ -8573,7 +8570,7 @@
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B325" s="3">
         <v>46409</v>
@@ -8596,7 +8593,7 @@
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B326" s="3">
         <v>46590</v>
@@ -8619,7 +8616,7 @@
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B327" s="3">
         <v>46682</v>
@@ -8642,7 +8639,7 @@
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B328" s="3">
         <v>46226</v>
@@ -8665,7 +8662,7 @@
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B329" s="3">
         <v>46410</v>
@@ -8688,7 +8685,7 @@
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B330" s="3">
         <v>46591</v>
@@ -8711,7 +8708,7 @@
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B331" s="3">
         <v>46775</v>
@@ -8734,7 +8731,7 @@
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B332" s="3">
         <v>46957</v>
@@ -8757,7 +8754,7 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B333" s="3">
         <v>47141</v>
@@ -8780,7 +8777,7 @@
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B334" s="3">
         <v>47322</v>
@@ -8803,7 +8800,7 @@
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B335" s="3">
         <v>47414</v>
@@ -8826,7 +8823,7 @@
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B336" s="3">
         <v>46094</v>
@@ -8849,7 +8846,7 @@
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B337" s="3">
         <v>46186</v>
@@ -8872,7 +8869,7 @@
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B338" s="3">
         <v>46111</v>
@@ -8895,7 +8892,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B339" s="3">
         <v>46203</v>
@@ -10160,7 +10157,7 @@
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B394" s="3">
         <v>46108</v>
@@ -10183,7 +10180,7 @@
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B395" s="3">
         <v>46292</v>
@@ -10206,7 +10203,7 @@
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B396" s="3">
         <v>46473</v>
@@ -10229,7 +10226,7 @@
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B397" s="3">
         <v>46657</v>
@@ -10252,7 +10249,7 @@
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B398" s="3">
         <v>46839</v>
@@ -10275,7 +10272,7 @@
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B399" s="3">
         <v>47023</v>
@@ -10298,7 +10295,7 @@
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B400" s="3">
         <v>47204</v>
@@ -10321,7 +10318,7 @@
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B401" s="3">
         <v>47388</v>
@@ -10344,7 +10341,7 @@
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B402" s="3">
         <v>46155</v>
@@ -10367,7 +10364,7 @@
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B403" s="3">
         <v>46339</v>
@@ -10390,7 +10387,7 @@
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B404" s="3">
         <v>46520</v>
@@ -10413,7 +10410,7 @@
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B405" s="3">
         <v>46704</v>
@@ -10436,7 +10433,7 @@
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B406" s="3">
         <v>46886</v>
@@ -10459,7 +10456,7 @@
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B407" s="3">
         <v>47070</v>
@@ -10482,7 +10479,7 @@
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B408" s="3">
         <v>47251</v>
@@ -10505,7 +10502,7 @@
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B409" s="3">
         <v>47435</v>
@@ -10528,7 +10525,7 @@
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B410" s="3">
         <v>47616</v>
@@ -10551,7 +10548,7 @@
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B411" s="3">
         <v>47800</v>
@@ -10574,7 +10571,7 @@
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B412" s="3">
         <v>47981</v>
@@ -10597,7 +10594,7 @@
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B413" s="3">
         <v>48165</v>
@@ -10620,7 +10617,7 @@
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B414" s="3">
         <v>46155</v>
@@ -10643,7 +10640,7 @@
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B415" s="3">
         <v>46339</v>
@@ -10666,7 +10663,7 @@
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B416" s="3">
         <v>46520</v>
@@ -10689,7 +10686,7 @@
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B417" s="3">
         <v>46704</v>
@@ -10712,7 +10709,7 @@
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B418" s="3">
         <v>46886</v>
@@ -10735,7 +10732,7 @@
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B419" s="3">
         <v>47070</v>
@@ -10758,7 +10755,7 @@
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B420" s="3">
         <v>46097</v>
@@ -10781,7 +10778,7 @@
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B421" s="3">
         <v>46129</v>
@@ -10804,7 +10801,7 @@
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B422" s="3">
         <v>46080</v>
@@ -10827,7 +10824,7 @@
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B423" s="3">
         <v>46171</v>
@@ -10850,7 +10847,7 @@
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B424" s="3">
         <v>46142</v>
@@ -10873,7 +10870,7 @@
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B425" s="3">
         <v>46356</v>
@@ -10896,7 +10893,7 @@
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B426" s="3">
         <v>46325</v>
@@ -10919,7 +10916,7 @@
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B427" s="3">
         <v>46265</v>
@@ -10942,7 +10939,7 @@
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B428" s="3">
         <v>46234</v>
@@ -10965,7 +10962,7 @@
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B429" s="3">
         <v>46066</v>
@@ -10988,7 +10985,7 @@
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B430" s="3">
         <v>46402</v>
@@ -11011,7 +11008,7 @@
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B431" s="3">
         <v>46507</v>
@@ -11034,7 +11031,7 @@
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B432" s="3">
         <v>46203</v>
@@ -11057,7 +11054,7 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B433" s="3">
         <v>46568</v>
@@ -11080,7 +11077,7 @@
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B434" s="3">
         <v>46538</v>
@@ -11103,7 +11100,7 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B435" s="3">
         <v>46221</v>
@@ -11126,7 +11123,7 @@
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B436" s="3">
         <v>46221</v>
@@ -11149,7 +11146,7 @@
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B437" s="3">
         <v>46405</v>
@@ -11172,7 +11169,7 @@
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B438" s="3">
         <v>46586</v>
@@ -11195,7 +11192,7 @@
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B439" s="3">
         <v>46770</v>
@@ -11218,7 +11215,7 @@
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B440" s="3">
         <v>46952</v>
@@ -11241,7 +11238,7 @@
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B441" s="3">
         <v>47136</v>
@@ -11264,7 +11261,7 @@
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B442" s="3">
         <v>47317</v>
@@ -11287,7 +11284,7 @@
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B443" s="3">
         <v>47501</v>
@@ -11310,7 +11307,7 @@
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B444" s="3">
         <v>47682</v>
@@ -11333,7 +11330,7 @@
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B445" s="3">
         <v>47866</v>
@@ -11356,7 +11353,7 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B446" s="3">
         <v>48047</v>
@@ -11394,7 +11391,7 @@
         <v>20</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>16</v>
@@ -11417,7 +11414,7 @@
         <v>20</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>16</v>
@@ -11425,7 +11422,7 @@
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B449" s="3">
         <v>46122</v>
@@ -11448,7 +11445,7 @@
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B450" s="3">
         <v>46305</v>
@@ -11471,7 +11468,7 @@
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B451" s="3">
         <v>46487</v>
@@ -11494,7 +11491,7 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B452" s="3">
         <v>46670</v>
@@ -11517,7 +11514,7 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B453" s="3">
         <v>46853</v>
@@ -11540,7 +11537,7 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B454" s="3">
         <v>47036</v>
@@ -11563,7 +11560,7 @@
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B455" s="3">
         <v>47218</v>
@@ -11586,7 +11583,7 @@
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B456" s="3">
         <v>47401</v>
@@ -11609,7 +11606,7 @@
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B457" s="3">
         <v>47583</v>
@@ -11632,7 +11629,7 @@
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B458" s="3">
         <v>47766</v>
@@ -11655,7 +11652,7 @@
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B459" s="3">
         <v>47948</v>
@@ -11678,7 +11675,7 @@
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B460" s="3">
         <v>48131</v>
@@ -11701,7 +11698,7 @@
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B461" s="3">
         <v>46183</v>
@@ -11724,7 +11721,7 @@
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B462" s="3">
         <v>46366</v>
@@ -11747,7 +11744,7 @@
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B463" s="3">
         <v>46548</v>
@@ -11770,7 +11767,7 @@
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B464" s="3">
         <v>46731</v>
@@ -11793,7 +11790,7 @@
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B465" s="3">
         <v>46914</v>
@@ -11816,7 +11813,7 @@
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B466" s="3">
         <v>47097</v>
@@ -11839,7 +11836,7 @@
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B467" s="3">
         <v>47279</v>
@@ -11862,7 +11859,7 @@
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B468" s="3">
         <v>47462</v>
@@ -11885,7 +11882,7 @@
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B469" s="3">
         <v>47644</v>
@@ -11908,7 +11905,7 @@
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B470" s="3">
         <v>47827</v>
@@ -11931,7 +11928,7 @@
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B471" s="3">
         <v>48009</v>
@@ -11954,7 +11951,7 @@
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B472" s="3">
         <v>48192</v>
@@ -11977,7 +11974,7 @@
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B473" s="3">
         <v>48375</v>
@@ -12000,7 +11997,7 @@
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B474" s="3">
         <v>48558</v>
@@ -12023,7 +12020,7 @@
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B475" s="3">
         <v>48740</v>
@@ -12046,7 +12043,7 @@
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B476" s="3">
         <v>48923</v>
@@ -12069,7 +12066,7 @@
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B477" s="3">
         <v>49105</v>
@@ -12092,7 +12089,7 @@
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B478" s="3">
         <v>49288</v>
@@ -12115,7 +12112,7 @@
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B479" s="3">
         <v>49470</v>
@@ -12138,7 +12135,7 @@
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B480" s="3">
         <v>49653</v>
@@ -12161,7 +12158,7 @@
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B481" s="3">
         <v>46128</v>
@@ -12184,7 +12181,7 @@
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B482" s="3">
         <v>46311</v>
@@ -12207,7 +12204,7 @@
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B483" s="3">
         <v>46493</v>
@@ -12230,7 +12227,7 @@
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B484" s="3">
         <v>46676</v>
@@ -12253,7 +12250,7 @@
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B485" s="3">
         <v>46859</v>
@@ -12276,7 +12273,7 @@
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B486" s="3">
         <v>47042</v>
@@ -12299,7 +12296,7 @@
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B487" s="3">
         <v>47224</v>
@@ -12322,7 +12319,7 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B488" s="3">
         <v>47407</v>
@@ -12345,7 +12342,7 @@
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B489" s="3">
         <v>47589</v>
@@ -12368,7 +12365,7 @@
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B490" s="3">
         <v>47772</v>
@@ -12391,7 +12388,7 @@
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B491" s="3">
         <v>47954</v>
@@ -12414,7 +12411,7 @@
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B492" s="3">
         <v>48137</v>
@@ -12437,7 +12434,7 @@
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B493" s="3">
         <v>48320</v>
@@ -12460,7 +12457,7 @@
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B494" s="3">
         <v>48503</v>
@@ -12483,7 +12480,7 @@
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B495" s="3">
         <v>46220</v>
@@ -12506,7 +12503,7 @@
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B496" s="3">
         <v>46404</v>
@@ -12529,7 +12526,7 @@
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B497" s="3">
         <v>46585</v>
@@ -12552,7 +12549,7 @@
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B498" s="3">
         <v>46769</v>
@@ -12575,7 +12572,7 @@
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B499" s="3">
         <v>46951</v>
@@ -12598,7 +12595,7 @@
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B500" s="3">
         <v>47135</v>
@@ -12621,7 +12618,7 @@
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B501" s="3">
         <v>47316</v>
@@ -12644,7 +12641,7 @@
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B502" s="3">
         <v>47500</v>
@@ -12667,7 +12664,7 @@
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B503" s="3">
         <v>47681</v>
@@ -12690,7 +12687,7 @@
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B504" s="3">
         <v>47865</v>
@@ -12713,7 +12710,7 @@
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B505" s="3">
         <v>48046</v>
@@ -12736,7 +12733,7 @@
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B506" s="3">
         <v>48230</v>
@@ -12759,7 +12756,7 @@
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B507" s="3">
         <v>48412</v>
@@ -12782,7 +12779,7 @@
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B508" s="3">
         <v>48596</v>
@@ -12805,7 +12802,7 @@
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B509" s="3">
         <v>48777</v>
@@ -12828,7 +12825,7 @@
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B510" s="3">
         <v>48961</v>
@@ -12851,7 +12848,7 @@
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B511" s="3">
         <v>46203</v>
@@ -12874,7 +12871,7 @@
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B512" s="3">
         <v>46386</v>
@@ -12897,7 +12894,7 @@
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B513" s="3">
         <v>46568</v>
@@ -12920,7 +12917,7 @@
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B514" s="3">
         <v>46751</v>
@@ -12943,7 +12940,7 @@
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B515" s="3">
         <v>46934</v>
@@ -12966,7 +12963,7 @@
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B516" s="3">
         <v>47117</v>
@@ -12989,7 +12986,7 @@
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B517" s="3">
         <v>47299</v>
@@ -13012,7 +13009,7 @@
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B518" s="3">
         <v>46111</v>
@@ -13035,7 +13032,7 @@
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B519" s="3">
         <v>46295</v>
@@ -13058,7 +13055,7 @@
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B520" s="3">
         <v>46476</v>
@@ -13081,7 +13078,7 @@
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B521" s="3">
         <v>46660</v>
@@ -13104,7 +13101,7 @@
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B522" s="3">
         <v>46842</v>
@@ -13127,7 +13124,7 @@
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B523" s="3">
         <v>47026</v>
@@ -13150,7 +13147,7 @@
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B524" s="3">
         <v>47207</v>
@@ -13173,7 +13170,7 @@
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B525" s="3">
         <v>47391</v>
@@ -13196,7 +13193,7 @@
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B526" s="3">
         <v>47572</v>
@@ -13219,7 +13216,7 @@
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B527" s="3">
         <v>47756</v>
@@ -13242,7 +13239,7 @@
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B528" s="3">
         <v>47937</v>
@@ -13265,7 +13262,7 @@
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B529" s="3">
         <v>48121</v>
@@ -13288,7 +13285,7 @@
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B530" s="3">
         <v>48303</v>
@@ -13311,7 +13308,7 @@
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B531" s="3">
         <v>48487</v>
@@ -13334,7 +13331,7 @@
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B532" s="3">
         <v>48668</v>
@@ -13357,7 +13354,7 @@
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B533" s="3">
         <v>48852</v>
@@ -13380,7 +13377,7 @@
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B534" s="3">
         <v>46081</v>
@@ -13403,7 +13400,7 @@
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B535" s="3">
         <v>46170</v>
@@ -13426,7 +13423,7 @@
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B536" s="3">
         <v>46092</v>
@@ -13449,7 +13446,7 @@
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B537" s="3">
         <v>46276</v>
@@ -13472,7 +13469,7 @@
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B538" s="3">
         <v>46457</v>
@@ -13495,7 +13492,7 @@
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B539" s="3">
         <v>46641</v>
@@ -13518,7 +13515,7 @@
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B540" s="3">
         <v>46823</v>
@@ -13541,7 +13538,7 @@
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B541" s="3">
         <v>47007</v>
@@ -13564,7 +13561,7 @@
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B542" s="3">
         <v>47188</v>
@@ -13587,7 +13584,7 @@
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B543" s="3">
         <v>47372</v>
@@ -13610,7 +13607,7 @@
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B544" s="3">
         <v>47553</v>
@@ -13633,7 +13630,7 @@
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B545" s="3">
         <v>47737</v>
@@ -13656,7 +13653,7 @@
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B546" s="3">
         <v>47918</v>
@@ -13679,7 +13676,7 @@
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B547" s="3">
         <v>48102</v>
